--- a/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>54862</x:v>
+        <x:v>50877</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>50877</x:v>
+        <x:v>55500</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>55500</x:v>
+        <x:v>61311</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -1077,7 +1077,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1136,7 +1136,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q3" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="R3" s="2" t="s">
         <x:v>46</x:v>
@@ -1189,7 +1189,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P4" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="Q4" s="0">
         <x:v>4000</x:v>
@@ -1245,7 +1245,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="P5" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="Q5" s="0">
         <x:v>4000</x:v>
@@ -1301,7 +1301,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P6" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="Q6" s="0">
         <x:v>4000</x:v>
@@ -1416,7 +1416,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q8" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="R8" s="3" t="s">
         <x:v>56</x:v>
@@ -1472,7 +1472,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q9" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="R9" s="5" t="s">
         <x:v>62</x:v>
@@ -1525,7 +1525,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P10" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="Q10" s="0">
         <x:v>4000</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q11" s="0">
-        <x:v>61311</x:v>
+        <x:v>60414</x:v>
       </x:c>
       <x:c r="R11" s="5" t="s">
         <x:v>62</x:v>

--- a/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -158,7 +158,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -173,43 +176,10 @@
     <x:t>Connection established</x:t>
   </x:si>
   <x:si>
-    <x:t>Connection acknowledged (ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>PSH, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client sending data</x:t>
-  </x:si>
-  <x:si>
-    <x:t>s001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client closing connection</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -236,7 +206,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -245,22 +215,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -283,7 +238,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="6">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -293,17 +248,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -313,18 +259,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -951,11 +885,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R11"/>
+  <x:dimension ref="A1:R8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -965,7 +899,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1062,28 +996,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1103,10 +1037,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1118,28 +1052,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="2" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q3" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1159,10 +1093,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1174,28 +1108,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1230,28 +1164,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="P5" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1271,10 +1205,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1286,28 +1220,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>56</x:v>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R6" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1342,7 +1276,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1362,8 +1296,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="4" t="s">
-        <x:v>58</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1383,10 +1317,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1398,196 +1332,28 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q8" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:18">
-      <x:c r="A9" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K9" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L9" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="M9" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N9" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P9" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="R9" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:18">
-      <x:c r="A10" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K10" s="0" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="L10" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="M10" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="N10" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="O10" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P10" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R10" s="5" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:18">
-      <x:c r="A11" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K11" s="0" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L11" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="M11" s="0" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="N11" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="O11" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>60414</x:v>
-      </x:c>
-      <x:c r="R11" s="5" t="s">
-        <x:v>62</x:v>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="2" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
+++ b/Run_Log/1/student/dungtdhe186461/TC5/GradeDetail.xlsx
@@ -158,18 +158,24 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
+    <x:t>SYN_SENT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PASS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SYN, ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Server responding (SYN-ACK)</x:t>
+  </x:si>
+  <x:si>
     <x:t>(MISSING - not captured)</x:t>
   </x:si>
   <x:si>
     <x:t>FAIL</x:t>
   </x:si>
   <x:si>
-    <x:t>SYN, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Server responding (SYN-ACK)</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -180,6 +186,18 @@
   </x:si>
   <x:si>
     <x:t>Data transfer in progress</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(Not validated by this test case)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RST-ACK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RESET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -206,7 +224,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -215,7 +233,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF90EE90"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -238,7 +266,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -248,8 +276,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -259,6 +293,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -885,11 +927,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R8"/>
+  <x:dimension ref="A1:R16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -996,25 +1038,25 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L2" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q2" s="0" t="s">
-        <x:v>17</x:v>
+      <x:c r="P2" s="0">
+        <x:v>36996</x:v>
+      </x:c>
+      <x:c r="Q2" s="0">
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
         <x:v>47</x:v>
@@ -1052,7 +1094,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1072,8 +1114,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R3" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1093,10 +1135,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1108,7 +1150,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1128,8 +1170,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R4" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1149,10 +1191,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>17</x:v>
@@ -1164,7 +1206,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1184,8 +1226,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R5" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1205,10 +1247,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1220,7 +1262,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1240,8 +1282,8 @@
       <x:c r="Q6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R6" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R6" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1261,10 +1303,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>17</x:v>
@@ -1276,7 +1318,7 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1296,8 +1338,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="R7" s="3" t="s">
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1317,10 +1359,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1332,28 +1374,476 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R8" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:18">
+      <x:c r="A9" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K9" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P9" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q9" s="0">
+        <x:v>36996</x:v>
+      </x:c>
+      <x:c r="R9" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:18">
+      <x:c r="A10" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L10" s="0" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="L8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="M8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="N8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="O8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="Q8" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="R8" s="2" t="s">
-        <x:v>47</x:v>
+      <x:c r="M10" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N10" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P10" s="0">
+        <x:v>54552</x:v>
+      </x:c>
+      <x:c r="Q10" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R10" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:18">
+      <x:c r="A11" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M11" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N11" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P11" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q11" s="0">
+        <x:v>54552</x:v>
+      </x:c>
+      <x:c r="R11" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:18">
+      <x:c r="A12" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K12" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L12" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M12" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N12" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P12" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q12" s="0">
+        <x:v>45850</x:v>
+      </x:c>
+      <x:c r="R12" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:18">
+      <x:c r="A13" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K13" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L13" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N13" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P13" s="0">
+        <x:v>58620</x:v>
+      </x:c>
+      <x:c r="Q13" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R13" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:18">
+      <x:c r="A14" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K14" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q14" s="0">
+        <x:v>58620</x:v>
+      </x:c>
+      <x:c r="R14" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:18">
+      <x:c r="A15" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B15" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K15" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="L15" s="0" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="M15" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N15" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="O15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P15" s="0">
+        <x:v>47324</x:v>
+      </x:c>
+      <x:c r="Q15" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="R15" s="4" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:18">
+      <x:c r="A16" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="J16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K16" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="L16" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="M16" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="N16" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="O16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="0">
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="Q16" s="0">
+        <x:v>47324</x:v>
+      </x:c>
+      <x:c r="R16" s="4" t="s">
+        <x:v>59</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
